--- a/results/mcdm/topsis_cc.xlsx
+++ b/results/mcdm/topsis_cc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,32 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CC_Baseline</t>
+          <t>CC_Baseline_L2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CC_DamageFocused</t>
+          <t>CC_Baseline_MinMax</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>CC_InfrastructureFocused</t>
+          <t>CC_DamageFocused_L2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>CC_DamageFocused_MinMax</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CC_InfrastructureFocused_L2</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CC_InfrastructureFocused_MinMax</t>
         </is>
       </c>
     </row>
@@ -455,17 +470,26 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2094079848413451</v>
+        <v>0.6008084112971983</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2074445827205587</v>
+        <v>0.5464753975417643</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2339251454345601</v>
+        <v>0.6980584972098188</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.650799229934529</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4415965828856851</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.368774831595134</v>
       </c>
     </row>
     <row r="3">
@@ -475,17 +499,26 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7086811738691273</v>
+        <v>0.7422887146010742</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7068720581961874</v>
+        <v>0.7107108319548023</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7327091967435662</v>
+        <v>0.8112334158672457</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7842120818568293</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.63619730235105</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5941239182998408</v>
       </c>
     </row>
     <row r="4">
@@ -495,17 +528,26 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2546157832643681</v>
+        <v>0.6051196389713975</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2548288706660272</v>
+        <v>0.5478419410400504</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2518675596501946</v>
+        <v>0.7019875182485785</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6521103931004234</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4434021430439554</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3692404041354663</v>
       </c>
     </row>
     <row r="5">
@@ -515,17 +557,26 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6048151381059117</v>
+        <v>0.7063701044469608</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5993360028654244</v>
+        <v>0.6967773373092474</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6822407807382436</v>
+        <v>0.7818222400995909</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7724068321702509</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.615496144735431</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5878092545725522</v>
       </c>
     </row>
     <row r="6">
@@ -535,17 +586,26 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5017184939879094</v>
+        <v>0.6668371845892396</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5017983440540872</v>
+        <v>0.6165861487092867</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5006927083565681</v>
+        <v>0.753116505861426</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7106792151467577</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5204984495579758</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4539119982198634</v>
       </c>
     </row>
     <row r="7">
@@ -555,17 +615,26 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1492392024691806</v>
+        <v>0.6017930091227937</v>
       </c>
       <c r="E7" t="n">
-        <v>0.152709347876989</v>
+        <v>0.5428223521529293</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0955394507237555</v>
+        <v>0.6991643314264362</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6475583404451359</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4385672717290158</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3639991935838122</v>
       </c>
     </row>
     <row r="8">
@@ -575,17 +644,26 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5959645548230378</v>
+        <v>0.7040661271370056</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5902300525048725</v>
+        <v>0.6958142516217007</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6773835569183614</v>
+        <v>0.7798915855198145</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7715731144226536</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6141381748274845</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5873846085662673</v>
       </c>
     </row>
     <row r="9">
@@ -595,17 +673,26 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3446711016329312</v>
+        <v>0.07507106200629729</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3485144123484323</v>
+        <v>0.05008946076687493</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2918287809629245</v>
+        <v>0.05573656342515106</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.03848644256212253</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.06818561727006545</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.04231749000205615</v>
       </c>
     </row>
     <row r="10">
@@ -615,17 +702,26 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1762848074734443</v>
+        <v>0.03387860947713795</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1803788444269646</v>
+        <v>0.02173590051309714</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1131684198151523</v>
+        <v>0.02507108835585041</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01672000198986103</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02992197761705067</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01690643326342339</v>
       </c>
     </row>
     <row r="11">
@@ -635,17 +731,26 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2458358474271173</v>
+        <v>0.07078015976160339</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2514805017196483</v>
+        <v>0.04577450339661825</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1593856120163915</v>
+        <v>0.05266880456163978</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.03535474083269745</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0626579177468079</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.03574326618493832</v>
       </c>
     </row>
     <row r="12">
@@ -655,17 +760,26 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7121908650779665</v>
+        <v>0.2298980385588393</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7105270224462379</v>
+        <v>0.2730499476416028</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7342318615945757</v>
+        <v>0.1671033005194793</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.203095949076504</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3407822544948947</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3887420067376774</v>
       </c>
     </row>
     <row r="13">
@@ -675,17 +789,26 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.5510866345322384</v>
+        <v>0.1617762481889156</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5534314532934231</v>
+        <v>0.1635356611506982</v>
       </c>
       <c r="F13" t="n">
-        <v>0.520819445701453</v>
+        <v>0.1182459860110583</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1219167285858503</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2067033269022513</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2152173320201652</v>
       </c>
     </row>
     <row r="14">
@@ -695,17 +818,26 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.8599753333399007</v>
+        <v>0.3734337259796744</v>
       </c>
       <c r="E14" t="n">
-        <v>0.856719130727946</v>
+        <v>0.4493195876941401</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9104346135014321</v>
+        <v>0.2797392449662446</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.345659292249998</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5487120705672767</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6319880781122204</v>
       </c>
     </row>
     <row r="15">
@@ -715,17 +847,26 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.8539051562942688</v>
+        <v>0.3723560187458405</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8505079544300211</v>
+        <v>0.4489634893962308</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9065008150572655</v>
+        <v>0.2788874942896973</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3453858758419625</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5480388183299212</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6317463622629131</v>
       </c>
     </row>
     <row r="16">
@@ -735,17 +876,26 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6876981932484236</v>
+        <v>0.2217621049334413</v>
       </c>
       <c r="E16" t="n">
-        <v>0.685050940152192</v>
+        <v>0.2702798054295971</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7233776017391824</v>
+        <v>0.1608294762259642</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2009362194988296</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3360479200012585</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3872726382292195</v>
       </c>
     </row>
     <row r="17">
@@ -755,17 +905,26 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7431471184605887</v>
+        <v>0.2437741801805834</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7428317599444573</v>
+        <v>0.2778922524034207</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7472220964162972</v>
+        <v>0.1779989403389799</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2069878784148226</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3487015136327785</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3911471539933009</v>
       </c>
     </row>
     <row r="18">
@@ -775,17 +934,26 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2646276280654895</v>
+        <v>0.2380899727521921</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2706686672450629</v>
+        <v>0.2077667197152795</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1721721653728168</v>
+        <v>0.2576244332567102</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2392883263780228</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1748698689656155</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1344800534091365</v>
       </c>
     </row>
     <row r="19">
@@ -795,17 +963,26 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.4406074368446545</v>
+        <v>0.2588929847274748</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4378945114924866</v>
+        <v>0.2623794963975524</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4756955499929444</v>
+        <v>0.2679248414582819</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2693024125254657</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2524591535021453</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2545536457798248</v>
       </c>
     </row>
     <row r="20">
@@ -815,17 +992,26 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3457316209966217</v>
+        <v>0.2365392358063292</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3496121917199996</v>
+        <v>0.2087253701977085</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2923445331822555</v>
+        <v>0.2568774797932102</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2400701388265574</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1747130286804796</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1365218801672865</v>
       </c>
     </row>
     <row r="21">
@@ -835,17 +1021,26 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.7000107957401153</v>
+        <v>0.3395855623718518</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6978491272312828</v>
+        <v>0.3683902539508671</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7289013031237941</v>
+        <v>0.3109267731541087</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3303084781214</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4062807866677073</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4375016386826577</v>
       </c>
     </row>
     <row r="22">
@@ -855,17 +1050,26 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2071271245521494</v>
+        <v>0.2271679497992638</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2119212605353285</v>
+        <v>0.2030739043182165</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1334807007567784</v>
+        <v>0.2518428488705231</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2367089030027472</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1645665958885832</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1304202687444379</v>
       </c>
     </row>
     <row r="23">
@@ -875,17 +1079,26 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6630969136416425</v>
+        <v>0.3302280826198096</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6595302261803129</v>
+        <v>0.3647417111958714</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7119141791137961</v>
+        <v>0.3055589900278051</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.3280538437111931</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3993849500121091</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.435296349971505</v>
       </c>
     </row>
     <row r="24">
@@ -895,17 +1108,26 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.2262186209776814</v>
+        <v>0.2299091119613829</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2314370881193557</v>
+        <v>0.2042285438431828</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1461917908224946</v>
+        <v>0.2533036221019747</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.2373529745599441</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1670945403512711</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1313911698853559</v>
       </c>
     </row>
     <row r="25">
@@ -915,17 +1137,26 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6494498742996218</v>
+        <v>0.4424498463850484</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6418421659410147</v>
+        <v>0.5296556044076618</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7666824472775141</v>
+        <v>0.378396822112981</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.4444527293762179</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6001436119292568</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6924855580002212</v>
       </c>
     </row>
     <row r="26">
@@ -935,17 +1166,26 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6428027976278652</v>
+        <v>0.4419961484107304</v>
       </c>
       <c r="E26" t="n">
-        <v>0.635099057818831</v>
+        <v>0.529419903877697</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7616964647151324</v>
+        <v>0.3781724934501824</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4443392637644306</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5995886602637792</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6922172877103254</v>
       </c>
     </row>
     <row r="27">
@@ -955,17 +1195,26 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5043629970532858</v>
+        <v>0.2075585300652259</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4968113287334942</v>
+        <v>0.2688036514245374</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6190227185439183</v>
+        <v>0.1526132165614673</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.2018832209909429</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3268892585734922</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.3865469381420252</v>
       </c>
     </row>
     <row r="28">
@@ -975,17 +1224,26 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5370977433153641</v>
+        <v>0.2079305695523082</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5299763717054725</v>
+        <v>0.2690014137236525</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6419835009756638</v>
+        <v>0.1527771147299105</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.201970207762122</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.327386430349479</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3867585444236694</v>
       </c>
     </row>
     <row r="29">
@@ -995,17 +1253,26 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5883336453230058</v>
+        <v>0.2103570195736315</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5823873797906088</v>
+        <v>0.2700589370065131</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6731108084832416</v>
+        <v>0.1541986400002171</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2025484544609327</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3297839483023868</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.387706081953556</v>
       </c>
     </row>
     <row r="30">
@@ -1015,17 +1282,26 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.4538470799566136</v>
+        <v>0.1421969123961629</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4517235980153724</v>
+        <v>0.1789064296407226</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4812306326091638</v>
+        <v>0.1045522531130127</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1344311971625576</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2176338495483368</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.2506851612257746</v>
       </c>
     </row>
     <row r="31">
@@ -1035,17 +1311,26 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4088748102567947</v>
+        <v>0.1375356000802142</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4048377256338559</v>
+        <v>0.1772466657468486</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4617933522706795</v>
+        <v>0.1013088186591579</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1332878502522661</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2145512360462969</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2496861503314594</v>
       </c>
     </row>
     <row r="32">
@@ -1055,17 +1340,26 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.04352077920758159</v>
+        <v>0.02582324928269194</v>
       </c>
       <c r="E32" t="n">
-        <v>0.04452648124120944</v>
+        <v>0.02371102122598148</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0276700769512138</v>
+        <v>0.02857185332436445</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.02732907108034512</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.01903539577099567</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.01537546114210651</v>
       </c>
     </row>
     <row r="33">
@@ -1075,17 +1369,26 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3919051649743064</v>
+        <v>0.2372904384780692</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3872536372615726</v>
+        <v>0.2562927990752233</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4537184517794333</v>
+        <v>0.2345860176483559</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.2457284453668846</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2634862810856948</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.282123353357264</v>
       </c>
     </row>
     <row r="34">
@@ -1095,17 +1398,26 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.14892804828179</v>
+        <v>0.1888754199820084</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1523909785465308</v>
+        <v>0.1711903109269184</v>
       </c>
       <c r="F34" t="n">
-        <v>0.09533747379352939</v>
+        <v>0.2101740068466713</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1990738010663312</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1372165612975547</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1102863481880715</v>
       </c>
     </row>
     <row r="35">
@@ -1115,17 +1427,26 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.6784864956114782</v>
+        <v>0.4253830768787309</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6713493314853344</v>
+        <v>0.5132279486629333</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7879565485540984</v>
+        <v>0.3534178763545528</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.4224153645176031</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5899898651512666</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6817234531257876</v>
       </c>
     </row>
     <row r="36">
@@ -1135,17 +1456,26 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.7804791719411184</v>
+        <v>0.4380060411353434</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7754086163565752</v>
+        <v>0.5188163076537894</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8582810592834003</v>
+        <v>0.3605746065467448</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4254434627184922</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6029275254631125</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6874801515646363</v>
       </c>
     </row>
     <row r="37">
@@ -1155,17 +1485,26 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.7444616572770478</v>
+        <v>0.4327450081684354</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7386107171866981</v>
+        <v>0.5166148081751121</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8340320633677903</v>
+        <v>0.3574434045656873</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.4241869535471058</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5979312730497188</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6853329111529968</v>
       </c>
     </row>
     <row r="38">
@@ -1175,17 +1514,26 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.4467640269788664</v>
+        <v>0.2284355111349819</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4443233717054065</v>
+        <v>0.2366044513892625</v>
       </c>
       <c r="F38" t="n">
-        <v>0.478283045755321</v>
+        <v>0.2301923045815197</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2346984051652902</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2361605282261473</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2438234673895218</v>
       </c>
     </row>
     <row r="39">
@@ -1195,17 +1543,26 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.6409040605672088</v>
+        <v>0.2997192278596122</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6365643981771275</v>
+        <v>0.3416724938968511</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7010558729095795</v>
+        <v>0.268845175766999</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.2971766458090604</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3823998539288004</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4248603029100241</v>
       </c>
     </row>
     <row r="40">
@@ -1215,17 +1572,26 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.6095818010303677</v>
+        <v>0.2951757507703758</v>
       </c>
       <c r="E40" t="n">
-        <v>0.604244341158061</v>
+        <v>0.3398321598750277</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6848148376196072</v>
+        <v>0.266270529087024</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.2960844658555347</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.378753228204783</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4236078772352912</v>
       </c>
     </row>
     <row r="41">
@@ -1235,17 +1601,26 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.5362947776622869</v>
+        <v>0.2896832720001555</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5291591887003054</v>
+        <v>0.337385442203408</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6414550095823677</v>
+        <v>0.2633197233483333</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.2947433627776754</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3736558652951977</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4217244235240163</v>
       </c>
     </row>
     <row r="42">
@@ -1255,17 +1630,26 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2345155278023361</v>
+        <v>0.198915291948616</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2399156079928115</v>
+        <v>0.1754652862352839</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1517543093701502</v>
+        <v>0.2154848474780685</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.2014379300757766</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1465977076884339</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1138993909797453</v>
       </c>
     </row>
     <row r="43">
@@ -1275,17 +1659,26 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.7699333976470126</v>
+        <v>0.4363797428445935</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7646304690225654</v>
+        <v>0.518151371522508</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8512314788726947</v>
+        <v>0.3595867551435833</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.4250550329673384</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.601434320438312</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6868482765423491</v>
       </c>
     </row>
     <row r="44">
@@ -1295,17 +1688,26 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.3523235820969183</v>
+        <v>0.2176024108519901</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3564330248307587</v>
+        <v>0.1993961388775284</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2955763636020117</v>
+        <v>0.2252274363315886</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.2147710923523754</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1836049241709676</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1606509553459048</v>
       </c>
     </row>
     <row r="45">
@@ -1315,17 +1717,26 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.6897611204880806</v>
+        <v>0.4264210127593975</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6828255427145056</v>
+        <v>0.5137327656187076</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7960259159064161</v>
+        <v>0.3539560858649832</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.422667243213071</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5911902555398317</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6822848681801764</v>
       </c>
     </row>
     <row r="46">
@@ -1335,17 +1746,26 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.103207972854562</v>
+        <v>0.1871629588783148</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1056056708961309</v>
+        <v>0.1705016618384983</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0658279807409497</v>
+        <v>0.2092157619162399</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.1986614608290574</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1358182477890863</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1097912634031637</v>
       </c>
     </row>
     <row r="47">
@@ -1355,17 +1775,26 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.4156347707932012</v>
+        <v>0.2001414982145467</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4118650049385296</v>
+        <v>0.1920092811100322</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4648578882731754</v>
+        <v>0.2159587284448341</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.2106191960791317</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.1684181226097185</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1554218151757595</v>
       </c>
     </row>
     <row r="48">
@@ -1375,17 +1804,26 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.7756750258825524</v>
+        <v>0.4372565682628602</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7704982645334942</v>
+        <v>0.5185114715196318</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8550743516958348</v>
+        <v>0.3601172318561692</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.4252644209051668</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.6022447699281483</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.6871922735383998</v>
       </c>
     </row>
     <row r="49">
@@ -1395,17 +1833,26 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.5369406005711485</v>
+        <v>0.2527927353060308</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5386465235545819</v>
+        <v>0.2465180065914853</v>
       </c>
       <c r="F49" t="n">
-        <v>0.514973881922693</v>
+        <v>0.2436108568445186</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.2406020579230212</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2548673903415491</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2497070669823935</v>
       </c>
     </row>
     <row r="50">
@@ -1415,17 +1862,26 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.6975120622973682</v>
+        <v>0.3128084633471175</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6952504358814039</v>
+        <v>0.3466916543834774</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7277914700645746</v>
+        <v>0.276589736600417</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3003491858543289</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3918694577527495</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4279212186602919</v>
       </c>
     </row>
     <row r="51">
@@ -1435,17 +1891,26 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.6062589142157651</v>
+        <v>0.421245272398527</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5981289965597262</v>
+        <v>0.511098418470198</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7332956814169994</v>
+        <v>0.3513899359515425</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.4213992577359144</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.584872579014687</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.679264511880183</v>
       </c>
     </row>
     <row r="52">
@@ -1455,17 +1920,26 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.5043629970532858</v>
+        <v>0.2890886952120017</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4968113287334942</v>
+        <v>0.3370879434274084</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6190227185439183</v>
+        <v>0.2630219249069327</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.2945942030964682</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.3730058986553652</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.4214675036582191</v>
       </c>
     </row>
     <row r="53">
@@ -1475,17 +1949,26 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.6396730685077096</v>
+        <v>0.4058329648544707</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6319258454041007</v>
+        <v>0.4963149704105163</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7593318876187394</v>
+        <v>0.3300192322012382</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.4025968240315391</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.574889443712</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.6689601840694507</v>
       </c>
     </row>
     <row r="54">
@@ -1495,17 +1978,26 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.5595410541429856</v>
+        <v>0.2679276905172503</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5528750661098899</v>
+        <v>0.3193112952038487</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6561982875164538</v>
+        <v>0.2338276426051422</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.2693740262201714</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3627957963412545</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.4136311682331158</v>
       </c>
     </row>
     <row r="55">
@@ -1515,17 +2007,26 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.4670758480034124</v>
+        <v>0.217132266140646</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4655534102526469</v>
+        <v>0.2369669978434951</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4866698609214108</v>
+        <v>0.2046644442685383</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.2173518875354427</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.2550846613557863</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.2748779785472708</v>
       </c>
     </row>
     <row r="56">
@@ -1535,17 +2036,26 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.5663442412917209</v>
+        <v>0.2683228085254166</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5598359593759232</v>
+        <v>0.3194930850355541</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6603164564208341</v>
+        <v>0.2340358036298431</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.2694702000201973</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.3631888769527921</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4137816843910435</v>
       </c>
     </row>
     <row r="57">
@@ -1555,17 +2065,26 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.2292822122692002</v>
+        <v>0.1665179150629003</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2345679557273377</v>
+        <v>0.1458992597281293</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1482428421855602</v>
+        <v>0.1788042536611629</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.1667680560420844</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1237040461573612</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.09491885905120308</v>
       </c>
     </row>
     <row r="58">
@@ -1575,17 +2094,26 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.63935312576686</v>
+        <v>0.2763985952315872</v>
       </c>
       <c r="E58" t="n">
-        <v>0.6349614466192083</v>
+        <v>0.3228069412613254</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7002777248263854</v>
+        <v>0.2386571967174196</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.2714160331539479</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.369912584965396</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.4161718848939689</v>
       </c>
     </row>
     <row r="59">
@@ -1595,17 +2123,26 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.7038023043390285</v>
+        <v>0.4106977802906875</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6971298525418459</v>
+        <v>0.4987014974827075</v>
       </c>
       <c r="F59" t="n">
-        <v>0.805949207705238</v>
+        <v>0.3325094925942147</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.4037694443426996</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.5806643390573709</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6716740903803148</v>
       </c>
     </row>
     <row r="60">
@@ -1615,17 +2152,26 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.3435931025628502</v>
+        <v>0.6066370544793768</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3473984146277774</v>
+        <v>0.5463102997025521</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2913057057344893</v>
+        <v>0.6974221724305664</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.6461644943359488</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.4470878921111071</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.3735878303324644</v>
       </c>
     </row>
     <row r="61">
@@ -1635,17 +2181,26 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.5440030517378478</v>
+        <v>0.6489984892669081</v>
       </c>
       <c r="E61" t="n">
-        <v>0.5460295502420024</v>
+        <v>0.5903458797866403</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5178800934152472</v>
+        <v>0.7306474535118999</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.682094307865312</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.4998471894444048</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.4311990434578359</v>
       </c>
     </row>
     <row r="62">
@@ -1655,17 +2210,26 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.4860124544098514</v>
+        <v>0.6427762110070653</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4853630662065789</v>
+        <v>0.6020402015574154</v>
       </c>
       <c r="F62" t="n">
-        <v>0.4943573870753133</v>
+        <v>0.725103740028761</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.6909355863041721</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.5112037803139167</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.4556534314464538</v>
       </c>
     </row>
     <row r="63">
@@ -1675,17 +2239,26 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.68403027810759</v>
+        <v>0.7019257115924743</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6812417022849506</v>
+        <v>0.6790474302211262</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7217050905877399</v>
+        <v>0.7684529920291608</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.7486169597075352</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.6075833173585019</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5745334892870647</v>
       </c>
     </row>
     <row r="64">
@@ -1695,17 +2268,26 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.4644255947845466</v>
+        <v>0.171334324609866</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4627819978293443</v>
+        <v>0.1888757829711</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4855859075905579</v>
+        <v>0.1573524881621358</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.1690558025101863</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.2074584718850099</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.2247396259775484</v>
       </c>
     </row>
     <row r="65">
@@ -1715,17 +2297,26 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.3006329996239001</v>
+        <v>0.1249697291706569</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3028204918008043</v>
+        <v>0.1107108888963542</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2713841069306002</v>
+        <v>0.133297062065873</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.1251612773858798</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.09503653711674095</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.07450483578601282</v>
       </c>
     </row>
     <row r="66">
@@ -1735,17 +2326,26 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.5419564854512707</v>
+        <v>0.2436179505490299</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5349244250837686</v>
+        <v>0.2998044019926983</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6451500542443342</v>
+        <v>0.2012067902826503</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.2423739785717307</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.3494400608592577</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.4041375153367213</v>
       </c>
     </row>
     <row r="67">
@@ -1755,17 +2355,26 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.566654458875178</v>
+        <v>0.2447299171366154</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5601535633658269</v>
+        <v>0.3003253262954205</v>
       </c>
       <c r="F67" t="n">
-        <v>0.660502326018738</v>
+        <v>0.2017865047590019</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.2426421450285157</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.3506070663384789</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.4045965269727936</v>
       </c>
     </row>
     <row r="68">
@@ -1775,17 +2384,26 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.2033132012433785</v>
+        <v>0.1244001717279674</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2080216337713654</v>
+        <v>0.1091870658882799</v>
       </c>
       <c r="F68" t="n">
-        <v>0.130954957039276</v>
+        <v>0.1329932812850276</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.1242733900146512</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.09304723706798815</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.07128073527858018</v>
       </c>
     </row>
     <row r="69">
@@ -1795,17 +2413,26 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.5905527876406966</v>
+        <v>0.3868710926624237</v>
       </c>
       <c r="E69" t="n">
-        <v>0.5823060088026135</v>
+        <v>0.4788647468149812</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7204485607265543</v>
+        <v>0.3064871006584408</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.3820238456662819</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.560179538910034</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.655597817305254</v>
       </c>
     </row>
     <row r="70">
@@ -1815,17 +2442,26 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.08033064791421793</v>
+        <v>0.1149297439778947</v>
       </c>
       <c r="E70" t="n">
-        <v>0.08219395890960324</v>
+        <v>0.1050458798928675</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05116409752809439</v>
+        <v>0.1280968484310663</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.1220511844824244</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.08381967081024561</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.06766483286849792</v>
       </c>
     </row>
     <row r="71">
@@ -1835,17 +2471,26 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.6870279885631952</v>
+        <v>0.2678138314066533</v>
       </c>
       <c r="E71" t="n">
-        <v>0.68435480000843</v>
+        <v>0.3110364717389092</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7230729359672374</v>
+        <v>0.2195036142380312</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.2521913576975946</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.3667462817729238</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.4110615749152287</v>
       </c>
     </row>
     <row r="72">
@@ -1855,17 +2500,26 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.471356180832279</v>
+        <v>0.1944998635028455</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4700300646178585</v>
+        <v>0.218622334210902</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4884155208570602</v>
+        <v>0.1746139117446434</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.1910747261583571</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.2441486552856283</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.2676675844995517</v>
       </c>
     </row>
     <row r="73">
@@ -1875,17 +2529,26 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.4598214966845214</v>
+        <v>0.1923415971282412</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4579682472039865</v>
+        <v>0.2178100238405164</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4836964229568707</v>
+        <v>0.1733412513111598</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.1905544031836778</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.242666457794469</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2672110855866303</v>
       </c>
     </row>
     <row r="74">
@@ -1895,17 +2558,26 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.8033623371170437</v>
+        <v>0.3501052790833199</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8058708372518318</v>
+        <v>0.3434922096067345</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7715706775905243</v>
+        <v>0.280011896492919</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.2773486562500686</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.4173003772192904</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.4267315257437071</v>
       </c>
     </row>
     <row r="75">
@@ -1915,17 +2587,26 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.6200380805032811</v>
+        <v>0.2541467980046025</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6150211048497022</v>
+        <v>0.3060034042549769</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6903632222943445</v>
+        <v>0.2107454253656195</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.2488390510387335</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.3572958612416121</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.4079548579371438</v>
       </c>
     </row>
     <row r="76">
@@ -1935,17 +2616,26 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.3866204500871379</v>
+        <v>0.2478528137838564</v>
       </c>
       <c r="E76" t="n">
-        <v>0.3946827698453738</v>
+        <v>0.1801908634154403</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2610210636973499</v>
+        <v>0.2138105025093565</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.1710869542549356</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.2081696123544908</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.1315995339545297</v>
       </c>
     </row>
     <row r="77">
@@ -1955,17 +2645,26 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.6233206438108405</v>
+        <v>0.3263494253548401</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6184069444766357</v>
+        <v>0.4015775666416392</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6920781281972993</v>
+        <v>0.2598792253959369</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.3182953140339315</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.4766084879330029</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.5553912651601054</v>
       </c>
     </row>
     <row r="78">
@@ -1975,17 +2674,26 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.5259170414198155</v>
+        <v>0.1857760651070022</v>
       </c>
       <c r="E78" t="n">
-        <v>0.527117726310968</v>
+        <v>0.1811536076811684</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5104752685534379</v>
+        <v>0.1704761690356389</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1686783249688113</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.1970091735081208</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.1947874680904404</v>
       </c>
     </row>
     <row r="79">
@@ -1995,17 +2703,26 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.2426405838297976</v>
+        <v>0.1416453753944069</v>
       </c>
       <c r="E79" t="n">
-        <v>0.248216607369834</v>
+        <v>0.1206585645097847</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1572264964607389</v>
+        <v>0.1467619454268338</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.1349491138033266</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.107920658614053</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.07973341614944068</v>
       </c>
     </row>
     <row r="80">
@@ -2015,17 +2732,26 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.3784993357669123</v>
+        <v>0.2380709958833142</v>
       </c>
       <c r="E80" t="n">
-        <v>0.386474700234041</v>
+        <v>0.1739785809761512</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2546344472046575</v>
+        <v>0.2068790669229997</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.1669587158130807</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.1990503753764282</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.1262723699367544</v>
       </c>
     </row>
     <row r="81">
@@ -2035,17 +2761,26 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.1438582816500888</v>
+        <v>0.5308238078914138</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1472035588409863</v>
+        <v>0.4753610093875333</v>
       </c>
       <c r="F81" t="n">
-        <v>0.09204902959591552</v>
+        <v>0.6210416596780824</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.5739646521516208</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.3775134978188415</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.3090299350351681</v>
       </c>
     </row>
     <row r="82">
@@ -2055,17 +2790,26 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.4302125767213562</v>
+        <v>0.5889485522151384</v>
       </c>
       <c r="E82" t="n">
-        <v>0.427049000305494</v>
+        <v>0.5604446109488184</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4712606908380749</v>
+        <v>0.6645434467015457</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.6413557127404195</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.4746494830419462</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.4298125267561348</v>
       </c>
     </row>
     <row r="83">
@@ -2075,17 +2819,26 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.06662475609676283</v>
+        <v>0.5268966299236851</v>
       </c>
       <c r="E83" t="n">
-        <v>0.06816824868705816</v>
+        <v>0.4741167820445234</v>
       </c>
       <c r="F83" t="n">
-        <v>0.04240366296939786</v>
+        <v>0.6176364623044974</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.5728001940893205</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.3758555561240503</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.3085985188478989</v>
       </c>
     </row>
     <row r="84">
@@ -2095,17 +2848,26 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.3354951748625876</v>
+        <v>0.5653673122347277</v>
       </c>
       <c r="E84" t="n">
-        <v>0.3390110276842435</v>
+        <v>0.5094193986483467</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2874139111318502</v>
+        <v>0.6484828991403909</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.6029418678952465</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.4150754859398431</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.346028994733501</v>
       </c>
     </row>
     <row r="85">
@@ -2115,17 +2877,26 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.3690547085880946</v>
+        <v>0.5816315352789054</v>
       </c>
       <c r="E85" t="n">
-        <v>0.3638014006401275</v>
+        <v>0.5576855803017237</v>
       </c>
       <c r="F85" t="n">
-        <v>0.4413451187345852</v>
+        <v>0.6586827013597844</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.6390046066731676</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.4708322049958798</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.4287207680452665</v>
       </c>
     </row>
     <row r="86">
@@ -2135,17 +2906,26 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.5043629970532858</v>
+        <v>0.6199725619668928</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4968113287334942</v>
+        <v>0.6252753159277299</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6190227185439183</v>
+        <v>0.6840874484746402</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.6855765967763146</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.5566530662245612</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.5477357033358774</v>
       </c>
     </row>
     <row r="87">
@@ -2155,17 +2935,26 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.1062163009603256</v>
+        <v>0.5284791792434403</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1086842695147149</v>
+        <v>0.4746172489002102</v>
       </c>
       <c r="F87" t="n">
-        <v>0.067760644952951</v>
+        <v>0.6190207654606592</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.5732743142484751</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.3765052618963291</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.3087625577052402</v>
       </c>
     </row>
     <row r="88">
@@ -2175,17 +2964,26 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.05908233605449288</v>
+        <v>0.5266868112176871</v>
       </c>
       <c r="E88" t="n">
-        <v>0.06045004704091488</v>
+        <v>0.4740505114349569</v>
       </c>
       <c r="F88" t="n">
-        <v>0.03758950417925794</v>
+        <v>0.617451674334119</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.5727368187816019</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.3757712998252098</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.3085777759123692</v>
       </c>
     </row>
     <row r="89">
@@ -2195,17 +2993,26 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.2821096447969754</v>
+        <v>0.5560670965622607</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2835343604597672</v>
+        <v>0.5062953511605133</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2633179587095097</v>
+        <v>0.6411055668027908</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.6003163291037464</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.4102231645815366</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.3445641958575705</v>
       </c>
     </row>
     <row r="90">
@@ -2215,17 +3022,26 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.7947771228285487</v>
+        <v>0.3632016746237152</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7900257423496231</v>
+        <v>0.445855113317193</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8677809059084878</v>
+        <v>0.2719706055205524</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.3431637561134318</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.541697201200588</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.6293726243094633</v>
       </c>
     </row>
     <row r="91">
@@ -2235,17 +3051,26 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.7919769230805166</v>
+        <v>0.335152538997335</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7940066712765346</v>
+        <v>0.3772652457437708</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7666329585661327</v>
+        <v>0.2489645334584813</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.2845805497023217</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.4731953680852621</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.5339772897350099</v>
       </c>
     </row>
     <row r="92">
@@ -2255,17 +3080,26 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.2018408618529477</v>
+        <v>0.05616813315255555</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1995273792254971</v>
+        <v>0.07342512975127566</v>
       </c>
       <c r="F92" t="n">
-        <v>0.230807648262026</v>
+        <v>0.04013956581368378</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.05435782535713173</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.08903132511186497</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.1030986180685283</v>
       </c>
     </row>
     <row r="93">
@@ -2275,17 +3109,26 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.7760001844288509</v>
+        <v>0.360778600057745</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7708305935120601</v>
+        <v>0.4449650841344924</v>
       </c>
       <c r="F93" t="n">
-        <v>0.8552916371197895</v>
+        <v>0.2702545579540434</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.3425790925501606</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.5397624045419261</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.6285891935502745</v>
       </c>
     </row>
     <row r="94">
@@ -2295,17 +3138,26 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.4634255596864169</v>
+        <v>0.1391888453827307</v>
       </c>
       <c r="E94" t="n">
-        <v>0.4617363318585</v>
+        <v>0.1750426843753136</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4851762203602392</v>
+        <v>0.1000636133557564</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.1296100640622422</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.2152869910051169</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.2483908822589443</v>
       </c>
     </row>
     <row r="95">
@@ -2315,17 +3167,26 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.1930715910896174</v>
+        <v>0.04133204386537045</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1975485660836248</v>
+        <v>0.02655832224149344</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1241929059281579</v>
+        <v>0.03062082477908712</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0204474038669042</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.03651795271983016</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.02067119219613572</v>
       </c>
     </row>
     <row r="96">
@@ -2335,17 +3196,26 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.2449689625203033</v>
+        <v>0.07022878620481815</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2505950297245529</v>
+        <v>0.04541114000417003</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1587994283257129</v>
+        <v>0.0522560301588853</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.03507382620966616</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.06216255440487431</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.03545424272884436</v>
       </c>
     </row>
     <row r="97">
@@ -2355,17 +3225,26 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.7420661796090132</v>
+        <v>0.3570171485888934</v>
       </c>
       <c r="E97" t="n">
-        <v>0.7361648291491789</v>
+        <v>0.4435082778480948</v>
       </c>
       <c r="F97" t="n">
-        <v>0.832400621960691</v>
+        <v>0.2677273579580868</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.3416819690001336</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.5364544946093633</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.6271967837718823</v>
       </c>
     </row>
     <row r="98">
@@ -2375,17 +3254,26 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.8512520135093338</v>
+        <v>0.3719517393393688</v>
       </c>
       <c r="E98" t="n">
-        <v>0.8477932588849725</v>
+        <v>0.4488735404334917</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9047794001573952</v>
+        <v>0.2785746894523475</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.3453271218692196</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.5478075901023433</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.6317003446131808</v>
       </c>
     </row>
     <row r="99">
@@ -2395,17 +3283,26 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.2360506334421233</v>
+        <v>0.01641629324743713</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2353902578460309</v>
+        <v>0.01597903193204969</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2444337832727272</v>
+        <v>0.01193398071914429</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.01194097984009258</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.02004497651283475</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.02018575531699473</v>
       </c>
     </row>
     <row r="100">
@@ -2415,17 +3312,26 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.2723424292664302</v>
+        <v>0.0312530183057973</v>
       </c>
       <c r="E100" t="n">
-        <v>0.2733478975582618</v>
+        <v>0.02336331710638324</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2591822092457379</v>
+        <v>0.02298650985857573</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0177138098772549</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.03092710288348688</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.02415509373517966</v>
       </c>
     </row>
     <row r="101">
@@ -2435,17 +3341,26 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.4332591230547432</v>
+        <v>0.1136212979738274</v>
       </c>
       <c r="E101" t="n">
-        <v>0.4302262906661025</v>
+        <v>0.1457954244796272</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4725700995923224</v>
+        <v>0.0814904958500923</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.1079118270290486</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.1783612916824061</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.2066996676858354</v>
       </c>
     </row>
     <row r="102">
@@ -2455,17 +3370,26 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.7241016420485816</v>
+        <v>0.234729695011437</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7229421384450234</v>
+        <v>0.2747445960841109</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7393211568871318</v>
+        <v>0.1708752022691633</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.2044480978118251</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.3435672624920948</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.3896150694647832</v>
       </c>
     </row>
     <row r="103">
@@ -2475,17 +3399,26 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.6104402239666809</v>
+        <v>0.207062547255143</v>
       </c>
       <c r="E103" t="n">
-        <v>0.6051285775618416</v>
+        <v>0.2652243293153277</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6852753672225126</v>
+        <v>0.1499623790698737</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.1972718130644313</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.3266476213960006</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.3841743176983417</v>
       </c>
     </row>
     <row r="104">
@@ -2495,17 +3428,26 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.3871451932123933</v>
+        <v>0.1321486185938966</v>
       </c>
       <c r="E104" t="n">
-        <v>0.3823410706611926</v>
+        <v>0.1725386467237348</v>
       </c>
       <c r="F104" t="n">
-        <v>0.4513218981370923</v>
+        <v>0.0950802826995432</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.1278766228906438</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.2106083382730801</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.2468622054149612</v>
       </c>
     </row>
     <row r="105">
@@ -2515,17 +3457,26 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.5716252993918041</v>
+        <v>0.20397422676636</v>
       </c>
       <c r="E105" t="n">
-        <v>0.5652449902700921</v>
+        <v>0.2640197646923944</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6634586942188858</v>
+        <v>0.1479273405103936</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.1965288191602384</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.324092077512508</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.3832172118045095</v>
       </c>
     </row>
     <row r="106">
@@ -2535,17 +3486,26 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.779322185858389</v>
+        <v>0.2688543172358649</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7807335634138906</v>
+        <v>0.287265938727442</v>
       </c>
       <c r="F106" t="n">
-        <v>0.761613556530865</v>
+        <v>0.1981621165417688</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.2147772072014457</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.3631165989669471</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.3955316972480309</v>
       </c>
     </row>
     <row r="107">
@@ -2555,17 +3515,26 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.5872891354028332</v>
+        <v>0.2049660484612154</v>
       </c>
       <c r="E107" t="n">
-        <v>0.5813145161542406</v>
+        <v>0.264424939448868</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6725196013353487</v>
+        <v>0.1485520330536723</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.1967659252219622</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.3249823988045948</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.3835604595392794</v>
       </c>
     </row>
     <row r="108">
@@ -2575,17 +3544,26 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.7464388220861725</v>
+        <v>0.3574577060444555</v>
       </c>
       <c r="E108" t="n">
-        <v>0.7406296493242708</v>
+        <v>0.4436847491946092</v>
       </c>
       <c r="F108" t="n">
-        <v>0.8353766889248154</v>
+        <v>0.2680131573098447</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.3417864334337862</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.5368648663289182</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.627373219685363</v>
       </c>
     </row>
     <row r="109">
@@ -2595,17 +3573,26 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.5043629970532858</v>
+        <v>0.2023658946762996</v>
       </c>
       <c r="E109" t="n">
-        <v>0.4968113287334942</v>
+        <v>0.2632603908916527</v>
       </c>
       <c r="F109" t="n">
-        <v>0.6190227185439183</v>
+        <v>0.1470723724296469</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.1961501810006925</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.3222672582461182</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.3824644461544278</v>
       </c>
     </row>
     <row r="110">
@@ -2615,17 +3602,26 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.6205760766002645</v>
+        <v>0.2082569980011419</v>
       </c>
       <c r="E110" t="n">
-        <v>0.6155759415750901</v>
+        <v>0.2656603240524184</v>
       </c>
       <c r="F110" t="n">
-        <v>0.6906451518457888</v>
+        <v>0.1507977146250499</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.1975624408618217</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.3275202326473857</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.3844847122332878</v>
       </c>
     </row>
     <row r="111">
@@ -2635,17 +3631,26 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.6257588773777054</v>
+        <v>0.2830524108618479</v>
       </c>
       <c r="E111" t="n">
-        <v>0.6209226954356382</v>
+        <v>0.3593628592209561</v>
       </c>
       <c r="F111" t="n">
-        <v>0.693343829437799</v>
+        <v>0.2078618267463338</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.2705059464012227</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.4416968967876946</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.5233975735409243</v>
       </c>
     </row>
     <row r="112">
@@ -2655,17 +3660,26 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.7390519684974129</v>
+        <v>0.3060056155409316</v>
       </c>
       <c r="E112" t="n">
-        <v>0.7385511019801454</v>
+        <v>0.3673930267280869</v>
       </c>
       <c r="F112" t="n">
-        <v>0.7455464422889807</v>
+        <v>0.2249544421748279</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.2762639149908555</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.4574348696627858</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.5291303082521845</v>
       </c>
     </row>
     <row r="113">
@@ -2675,17 +3689,26 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.4028471013704302</v>
+        <v>0.2211799560711202</v>
       </c>
       <c r="E113" t="n">
-        <v>0.3985812353544742</v>
+        <v>0.2429090513009903</v>
       </c>
       <c r="F113" t="n">
-        <v>0.4589956661502269</v>
+        <v>0.2146882453853677</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.2278362804710465</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.255264419528538</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.2766444746224682</v>
       </c>
     </row>
     <row r="114">
@@ -2695,17 +3718,26 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.6908711616979631</v>
+        <v>0.4162001989106097</v>
       </c>
       <c r="E114" t="n">
-        <v>0.6839559201338579</v>
+        <v>0.5043188106443571</v>
       </c>
       <c r="F114" t="n">
-        <v>0.7968153157444273</v>
+        <v>0.340683472287017</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.4111420220865898</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.5840579510521788</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.6755124414005338</v>
       </c>
     </row>
     <row r="115">
@@ -2715,17 +3747,26 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.5043629970532858</v>
+        <v>0.3429943513401791</v>
       </c>
       <c r="E115" t="n">
-        <v>0.4968113287334942</v>
+        <v>0.4192210461525842</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6190227185439183</v>
+        <v>0.2882650755660466</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.3439024647213598</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.4838985511465561</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.5651433852870298</v>
       </c>
     </row>
     <row r="116">
@@ -2735,17 +3776,26 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.1833161156487727</v>
+        <v>0.1720782887312206</v>
       </c>
       <c r="E116" t="n">
-        <v>0.1875710337560564</v>
+        <v>0.1544804660624982</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1177776960997116</v>
+        <v>0.1899697068104153</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.1792282664755621</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.1255236519977889</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.09948225975270267</v>
       </c>
     </row>
     <row r="117">
@@ -2755,17 +3805,26 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.6266889881667128</v>
+        <v>0.3511105376207404</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6218825560920865</v>
+        <v>0.4230857242619299</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6938248544948875</v>
+        <v>0.2925307815014437</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.3458706526228245</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4928584614916275</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.5690341015135443</v>
       </c>
     </row>
     <row r="118">
@@ -2775,17 +3834,26 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.5124523097094865</v>
+        <v>0.3430423301471955</v>
       </c>
       <c r="E118" t="n">
-        <v>0.5049749918392259</v>
+        <v>0.419247299731671</v>
       </c>
       <c r="F118" t="n">
-        <v>0.6249993197419034</v>
+        <v>0.2882869813280611</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.3439143295933206</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4839622887980452</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5651728549745108</v>
       </c>
     </row>
     <row r="119">
@@ -2795,17 +3863,26 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.1508030221129695</v>
+        <v>0.1694698703587626</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1543094192315953</v>
+        <v>0.1533801154457004</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0965548287776657</v>
+        <v>0.188592701939404</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.1786179769262557</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.1231056143617829</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.09856750356056543</v>
       </c>
     </row>
     <row r="120">
@@ -2815,17 +3892,26 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.1612500444735789</v>
+        <v>0.1701544933631427</v>
       </c>
       <c r="E120" t="n">
-        <v>0.164998119181705</v>
+        <v>0.1536663443048323</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1033499356273825</v>
+        <v>0.1889571451001919</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.1787786318791466</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.1237282777213992</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.09880013812638067</v>
       </c>
     </row>
     <row r="121">
@@ -2835,17 +3921,26 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.5043629970532858</v>
+        <v>0.3712190964335705</v>
       </c>
       <c r="E121" t="n">
-        <v>0.4968113287334942</v>
+        <v>0.4437332888737963</v>
       </c>
       <c r="F121" t="n">
-        <v>0.6190227185439183</v>
+        <v>0.3266242011899058</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3767681904444041</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.5008133092215316</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.5794277638061731</v>
       </c>
     </row>
     <row r="122">
@@ -2855,17 +3950,26 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.3980702453381549</v>
+        <v>0.260128101728138</v>
       </c>
       <c r="E122" t="n">
-        <v>0.3936307516170077</v>
+        <v>0.2748673044638005</v>
       </c>
       <c r="F122" t="n">
-        <v>0.4567269211241392</v>
+        <v>0.2634082187240038</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.2715550235582587</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.2751892985189369</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2895116939801471</v>
       </c>
     </row>
     <row r="123">
@@ -2875,17 +3979,26 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.2015362274179189</v>
+        <v>0.2239247673845852</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1992096295859561</v>
+        <v>0.213542999316361</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2306769911301433</v>
+        <v>0.2452247460281025</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.2383750309388331</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.1831775724963526</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.1663054333084809</v>
       </c>
     </row>
     <row r="124">
@@ -2895,17 +4008,26 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.4115680672427863</v>
+        <v>0.260886350892531</v>
       </c>
       <c r="E124" t="n">
-        <v>0.4076362413728304</v>
+        <v>0.2751937993946403</v>
       </c>
       <c r="F124" t="n">
-        <v>0.4630228127427035</v>
+        <v>0.2638286476158073</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.2717458888189234</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.2758083865641784</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.2897180645146863</v>
       </c>
     </row>
     <row r="125">
@@ -2915,17 +4037,26 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.5997160738367378</v>
+        <v>0.4354660872848166</v>
       </c>
       <c r="E125" t="n">
-        <v>0.5915317897836038</v>
+        <v>0.5240844496542347</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7279988149404347</v>
+        <v>0.3711317252801475</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4384942380980717</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5941181510082494</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.6880063081682484</v>
       </c>
     </row>
     <row r="126">
@@ -2935,17 +4066,26 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.4691942380336866</v>
+        <v>0.2674656880360233</v>
       </c>
       <c r="E126" t="n">
-        <v>0.4677688690270519</v>
+        <v>0.27790230153066</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4875345379280199</v>
+        <v>0.2674267359235443</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.2733392314243915</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.2809645733075219</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.2913672852203383</v>
       </c>
     </row>
     <row r="127">
@@ -2955,17 +4095,26 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.4040719805016026</v>
+        <v>0.2604348030256464</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3998517842875266</v>
+        <v>0.2750001057543154</v>
       </c>
       <c r="F127" t="n">
-        <v>0.4595697144873352</v>
+        <v>0.2635785940264364</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.2716326073979275</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.2754409584290573</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.2895959939153842</v>
       </c>
     </row>
     <row r="128">
@@ -2975,17 +4124,26 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.3911077950304298</v>
+        <v>0.2598323141616634</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3864299740487474</v>
+        <v>0.2747380930094805</v>
       </c>
       <c r="F128" t="n">
-        <v>0.4533218370523611</v>
+        <v>0.2632434168062627</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.2714796132083365</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2749446779663154</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.2894291241148204</v>
       </c>
     </row>
     <row r="129">
@@ -2995,17 +4153,26 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.5120162887815024</v>
+        <v>0.1560064987414002</v>
       </c>
       <c r="E129" t="n">
-        <v>0.5125742841524595</v>
+        <v>0.1817915249241897</v>
       </c>
       <c r="F129" t="n">
-        <v>0.5048464016523345</v>
+        <v>0.1132051217950424</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.13524093217041</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.2252515253373968</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.2519731666266696</v>
       </c>
     </row>
     <row r="130">
@@ -3015,17 +4182,26 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.4914352223353974</v>
+        <v>0.1481033903293391</v>
       </c>
       <c r="E130" t="n">
-        <v>0.4910373802254267</v>
+        <v>0.1790629288133722</v>
       </c>
       <c r="F130" t="n">
-        <v>0.4965466458826159</v>
+        <v>0.1071897221345764</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.1331064501726036</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2207697709518712</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.2506457895596043</v>
       </c>
     </row>
     <row r="131">
@@ -3035,17 +4211,26 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.02100728212272394</v>
+        <v>0.0104946937942793</v>
       </c>
       <c r="E131" t="n">
-        <v>0.02149130548903027</v>
+        <v>0.009659810311057724</v>
       </c>
       <c r="F131" t="n">
-        <v>0.01334531244699024</v>
+        <v>0.01159094675873984</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.01110177081386012</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.007756892762898059</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.006281667072633693</v>
       </c>
     </row>
     <row r="132">
@@ -3055,17 +4240,26 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.6211474977923768</v>
+        <v>0.2102442920751815</v>
       </c>
       <c r="E132" t="n">
-        <v>0.6161652866569389</v>
+        <v>0.2677926866949495</v>
       </c>
       <c r="F132" t="n">
-        <v>0.6909442247417587</v>
+        <v>0.1526444662083909</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.199594227348714</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.329429881565522</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3861318188547202</v>
       </c>
     </row>
     <row r="133">
@@ -3075,17 +4269,26 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.6358515294314018</v>
+        <v>0.3526757581695653</v>
       </c>
       <c r="E133" t="n">
-        <v>0.6280527926167701</v>
+        <v>0.4433235964078843</v>
       </c>
       <c r="F133" t="n">
-        <v>0.756429206362032</v>
+        <v>0.2662211727236061</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.3428601875803073</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.5313621546303072</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.6263648307310713</v>
       </c>
     </row>
     <row r="134">
@@ -3095,17 +4298,26 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.2290966327816494</v>
+        <v>0.06168176673244158</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2343783079733227</v>
+        <v>0.04031350183524884</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1481185035778918</v>
+        <v>0.04664874135355391</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.0321907434955696</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.05415630351151839</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.03107489588339184</v>
       </c>
     </row>
     <row r="135">
@@ -3115,17 +4327,26 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.1744446333221186</v>
+        <v>0.0349111113579878</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1784964620414137</v>
+        <v>0.02339639043034768</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1119640251082753</v>
+        <v>0.02723021507394424</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.01979819182939841</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.03032972852364892</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.01768385087754609</v>
       </c>
     </row>
     <row r="136">
@@ -3135,17 +4356,26 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.1727723636250836</v>
+        <v>0.1623499239596492</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1767858002194349</v>
+        <v>0.1461521190700388</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1108701896401082</v>
+        <v>0.1793561305301635</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.1694805950180229</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.1184926475612624</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.09417134543073526</v>
       </c>
     </row>
     <row r="137">
@@ -3155,17 +4385,26 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.1638644273243421</v>
+        <v>0.1616012753571504</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1676728311059437</v>
+        <v>0.1458343707999498</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1050538046801552</v>
+        <v>0.1789635567823791</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.1693058413936336</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.1177895224971771</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.09390386980084965</v>
       </c>
     </row>
     <row r="138">
@@ -3175,17 +4414,26 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.4807778333032887</v>
+        <v>0.2234399624066419</v>
       </c>
       <c r="E138" t="n">
-        <v>0.4798861047017172</v>
+        <v>0.2409000827405633</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4922402717240629</v>
+        <v>0.2107285720429722</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.2219806230832394</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.2588509233043205</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.2766350689471186</v>
       </c>
     </row>
     <row r="139">
@@ -3195,17 +4443,26 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.6835757260299312</v>
+        <v>0.4110459643611504</v>
       </c>
       <c r="E139" t="n">
-        <v>0.676528405654177</v>
+        <v>0.4998698416315542</v>
       </c>
       <c r="F139" t="n">
-        <v>0.7916108292994749</v>
+        <v>0.3343908597456223</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.4058251028923049</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5801419985276007</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.6722004417036733</v>
       </c>
     </row>
     <row r="140">
@@ -3215,17 +4472,26 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.2244190328945791</v>
+        <v>0.1715431462938078</v>
       </c>
       <c r="E140" t="n">
-        <v>0.2231918876201524</v>
+        <v>0.1670981936382539</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2398552386459408</v>
+        <v>0.1838729296447244</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.1807369049927518</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.1500308423428265</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.1425700432518422</v>
       </c>
     </row>
     <row r="141">
@@ -3235,17 +4501,26 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.5905527876406966</v>
+        <v>0.4066268558062274</v>
       </c>
       <c r="E141" t="n">
-        <v>0.5823060088026135</v>
+        <v>0.4976085218222411</v>
       </c>
       <c r="F141" t="n">
-        <v>0.7204485607265543</v>
+        <v>0.332234204982763</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.4047519717586665</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.5746279492518322</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.6695602056862151</v>
       </c>
     </row>
   </sheetData>
